--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="250">
   <si>
     <t>DOCUMENT CONTROL SECTION</t>
   </si>
@@ -2154,7 +2154,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -2234,15 +2234,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2398,7 +2389,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2410,34 +2401,34 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2534,7 +2525,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2797,19 +2788,34 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2891,10 +2897,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3322,190 +3328,190 @@
   <sheetData>
     <row r="1" ht="59.15" customHeight="1"/>
     <row r="2" ht="15.75" spans="1:6">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="117"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
+      <c r="A3" s="122"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="124"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="122"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="127"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="123" t="s">
+      <c r="B6" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="C6" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="123" t="s">
+      <c r="D6" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="123" t="s">
+      <c r="E6" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="122"/>
+      <c r="F6" s="127"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="C7" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="125" t="s">
+      <c r="D7" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="122"/>
+      <c r="F7" s="127"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="122"/>
+      <c r="B8" s="131"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="127"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="122"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="127"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="124"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="122"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="127"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="124"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="122"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="127"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="124"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="122"/>
+      <c r="A12" s="129"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="127"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="130"/>
-      <c r="B13" s="130"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
+      <c r="A13" s="135"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="131"/>
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="127"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="129" t="s">
+      <c r="A15" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="128" t="s">
+      <c r="B15" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="129" t="s">
+      <c r="C15" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="133"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="122"/>
+      <c r="A16" s="138"/>
+      <c r="B16" s="139"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="127"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="129" t="s">
+      <c r="A17" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="128" t="s">
+      <c r="B17" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="129" t="s">
+      <c r="C17" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="135"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="133"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="122"/>
+      <c r="A18" s="138"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="127"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="132"/>
+      <c r="B19" s="137"/>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -3530,570 +3536,570 @@
   <dimension ref="A1:G50"/>
   <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6" style="109" customWidth="1"/>
-    <col min="2" max="2" width="26.2666666666667" style="110" customWidth="1"/>
-    <col min="3" max="3" width="42.1809523809524" style="110" customWidth="1"/>
-    <col min="4" max="4" width="10.2666666666667" style="110" customWidth="1"/>
-    <col min="5" max="5" width="44.9047619047619" style="110" customWidth="1"/>
-    <col min="6" max="16384" width="8.72380952380952" style="110"/>
+    <col min="1" max="1" width="6" style="114" customWidth="1"/>
+    <col min="2" max="2" width="26.2666666666667" style="115" customWidth="1"/>
+    <col min="3" max="3" width="42.1809523809524" style="115" customWidth="1"/>
+    <col min="4" max="4" width="10.2666666666667" style="115" customWidth="1"/>
+    <col min="5" max="5" width="44.9047619047619" style="115" customWidth="1"/>
+    <col min="6" max="16384" width="8.72380952380952" style="115"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" spans="1:7">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="105" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="111">
+      <c r="A2" s="116">
         <v>1</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
     </row>
     <row r="3" ht="31.5" spans="1:7">
-      <c r="A3" s="111">
+      <c r="A3" s="116">
         <v>1.1</v>
       </c>
-      <c r="B3" s="113"/>
-      <c r="C3" s="112" t="s">
+      <c r="B3" s="118"/>
+      <c r="C3" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="G3" s="114"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="G3" s="119"/>
     </row>
     <row r="4" ht="25.5" spans="1:7">
-      <c r="A4" s="111">
+      <c r="A4" s="116">
         <v>1.2</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="112" t="s">
+      <c r="B4" s="118"/>
+      <c r="C4" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="111">
+      <c r="A5" s="116">
         <v>1.3</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="112" t="s">
+      <c r="B5" s="118"/>
+      <c r="C5" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="111">
+      <c r="A6" s="116">
         <v>2</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
     </row>
     <row r="7" ht="25.5" spans="1:7">
-      <c r="A7" s="111">
+      <c r="A7" s="116">
         <v>2.1</v>
       </c>
-      <c r="B7" s="113"/>
-      <c r="C7" s="112" t="s">
+      <c r="B7" s="118"/>
+      <c r="C7" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="98"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="103"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="111">
+      <c r="A8" s="116">
         <v>2.2</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="112" t="s">
+      <c r="B8" s="118"/>
+      <c r="C8" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="111">
+      <c r="A9" s="116">
         <v>2.3</v>
       </c>
-      <c r="B9" s="113"/>
-      <c r="C9" s="112" t="s">
+      <c r="B9" s="118"/>
+      <c r="C9" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="113"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="111">
+      <c r="A10" s="116">
         <v>2.4</v>
       </c>
-      <c r="B10" s="113"/>
-      <c r="C10" s="112" t="s">
+      <c r="B10" s="118"/>
+      <c r="C10" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="111">
+      <c r="A11" s="116">
         <v>2.5</v>
       </c>
-      <c r="B11" s="113"/>
-      <c r="C11" s="112" t="s">
+      <c r="B11" s="118"/>
+      <c r="C11" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="113"/>
-      <c r="E11" s="113"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="111">
+      <c r="A12" s="116">
         <v>2.6</v>
       </c>
-      <c r="B12" s="113"/>
-      <c r="C12" s="112" t="s">
+      <c r="B12" s="118"/>
+      <c r="C12" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="111">
+      <c r="A13" s="116">
         <v>3</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="111">
+      <c r="A14" s="116">
         <v>3.1</v>
       </c>
-      <c r="B14" s="113"/>
-      <c r="C14" s="112" t="s">
+      <c r="B14" s="118"/>
+      <c r="C14" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="111">
+      <c r="A15" s="116">
         <v>3.2</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="112" t="s">
+      <c r="B15" s="118"/>
+      <c r="C15" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="111">
+      <c r="A16" s="116">
         <v>3.3</v>
       </c>
-      <c r="B16" s="113"/>
-      <c r="C16" s="112" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
     </row>
     <row r="17" ht="25.5" spans="1:5">
-      <c r="A17" s="111">
+      <c r="A17" s="116">
         <v>3.4</v>
       </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="112" t="s">
+      <c r="B17" s="118"/>
+      <c r="C17" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="111">
+      <c r="A18" s="116">
         <v>4</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="111">
+      <c r="A19" s="116">
         <v>4.1</v>
       </c>
-      <c r="B19" s="113"/>
-      <c r="C19" s="104" t="s">
+      <c r="B19" s="118"/>
+      <c r="C19" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
     </row>
     <row r="20" ht="25.5" spans="1:5">
-      <c r="A20" s="111">
+      <c r="A20" s="116">
         <v>4.2</v>
       </c>
-      <c r="B20" s="113"/>
-      <c r="C20" s="112" t="s">
+      <c r="B20" s="118"/>
+      <c r="C20" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="113"/>
-      <c r="E20" s="113"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
     </row>
     <row r="21" ht="25.5" spans="1:5">
-      <c r="A21" s="111">
+      <c r="A21" s="116">
         <v>4.3</v>
       </c>
-      <c r="B21" s="113"/>
-      <c r="C21" s="112" t="s">
+      <c r="B21" s="118"/>
+      <c r="C21" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="111">
+      <c r="A22" s="116">
         <v>5</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="113"/>
-      <c r="D22" s="113"/>
-      <c r="E22" s="113"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="111">
+      <c r="A23" s="116">
         <v>5.1</v>
       </c>
-      <c r="B23" s="113"/>
-      <c r="C23" s="104" t="s">
+      <c r="B23" s="118"/>
+      <c r="C23" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="111">
+      <c r="A24" s="116">
         <v>5.2</v>
       </c>
-      <c r="B24" s="113"/>
-      <c r="C24" s="112" t="s">
+      <c r="B24" s="118"/>
+      <c r="C24" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="111">
+      <c r="A25" s="116">
         <v>6</v>
       </c>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="113"/>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="111">
+      <c r="A26" s="116">
         <v>6.1</v>
       </c>
-      <c r="B26" s="113"/>
-      <c r="C26" s="104" t="s">
+      <c r="B26" s="118"/>
+      <c r="C26" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
     </row>
     <row r="27" ht="25.5" spans="1:5">
-      <c r="A27" s="111">
+      <c r="A27" s="116">
         <v>6.2</v>
       </c>
-      <c r="B27" s="113"/>
-      <c r="C27" s="112" t="s">
+      <c r="B27" s="118"/>
+      <c r="C27" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="113"/>
-      <c r="E27" s="113"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="111">
+      <c r="A28" s="116">
         <v>7</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="113"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="113"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
     </row>
     <row r="29" ht="25.5" spans="1:5">
-      <c r="A29" s="111">
+      <c r="A29" s="116">
         <v>7.1</v>
       </c>
-      <c r="B29" s="113"/>
-      <c r="C29" s="104" t="s">
+      <c r="B29" s="118"/>
+      <c r="C29" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="113"/>
-      <c r="E29" s="113"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
     </row>
     <row r="30" ht="25.5" spans="1:5">
-      <c r="A30" s="111">
+      <c r="A30" s="116">
         <v>7.2</v>
       </c>
-      <c r="B30" s="113"/>
-      <c r="C30" s="112" t="s">
+      <c r="B30" s="118"/>
+      <c r="C30" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="111">
+      <c r="A31" s="116">
         <v>8</v>
       </c>
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="113"/>
-      <c r="D31" s="113"/>
-      <c r="E31" s="113"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
     </row>
     <row r="32" ht="25.5" spans="1:5">
-      <c r="A32" s="111">
+      <c r="A32" s="116">
         <v>8.1</v>
       </c>
-      <c r="B32" s="113"/>
-      <c r="C32" s="104" t="s">
+      <c r="B32" s="118"/>
+      <c r="C32" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="111">
+      <c r="A33" s="116">
         <v>8.2</v>
       </c>
-      <c r="B33" s="113"/>
-      <c r="C33" s="112" t="s">
+      <c r="B33" s="118"/>
+      <c r="C33" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="111">
+      <c r="A34" s="116">
         <v>8.3</v>
       </c>
-      <c r="B34" s="113"/>
-      <c r="C34" s="112" t="s">
+      <c r="B34" s="118"/>
+      <c r="C34" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
     </row>
     <row r="35" ht="25.5" spans="1:5">
-      <c r="A35" s="111">
+      <c r="A35" s="116">
         <v>9</v>
       </c>
-      <c r="B35" s="112" t="s">
+      <c r="B35" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="113"/>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="111">
+      <c r="A36" s="116">
         <v>9.1</v>
       </c>
-      <c r="B36" s="113"/>
-      <c r="C36" s="104" t="s">
+      <c r="B36" s="118"/>
+      <c r="C36" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="111">
+      <c r="A37" s="116">
         <v>9.2</v>
       </c>
-      <c r="B37" s="113"/>
-      <c r="C37" s="104" t="s">
+      <c r="B37" s="118"/>
+      <c r="C37" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="113"/>
-      <c r="E37" s="113"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="111">
+      <c r="A38" s="116">
         <v>9.3</v>
       </c>
-      <c r="B38" s="113"/>
-      <c r="C38" s="104" t="s">
+      <c r="B38" s="118"/>
+      <c r="C38" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
     </row>
     <row r="39" ht="25.5" spans="1:5">
-      <c r="A39" s="111">
+      <c r="A39" s="116">
         <v>10</v>
       </c>
-      <c r="B39" s="112" t="s">
+      <c r="B39" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="113"/>
-      <c r="D39" s="113"/>
-      <c r="E39" s="113"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
     </row>
     <row r="40" ht="25.5" spans="1:5">
-      <c r="A40" s="111">
+      <c r="A40" s="116">
         <v>10.1</v>
       </c>
-      <c r="B40" s="113"/>
-      <c r="C40" s="104" t="s">
+      <c r="B40" s="118"/>
+      <c r="C40" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="113"/>
-      <c r="E40" s="113"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
     </row>
     <row r="41" ht="25.5" spans="1:5">
-      <c r="A41" s="111">
+      <c r="A41" s="116">
         <v>10.2</v>
       </c>
-      <c r="B41" s="113"/>
-      <c r="C41" s="104" t="s">
+      <c r="B41" s="118"/>
+      <c r="C41" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="113"/>
-      <c r="E41" s="113"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="111">
+      <c r="A42" s="116">
         <v>11</v>
       </c>
-      <c r="B42" s="112" t="s">
+      <c r="B42" s="117" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="113"/>
-      <c r="D42" s="113"/>
-      <c r="E42" s="113"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="111">
+      <c r="A43" s="116">
         <v>11.1</v>
       </c>
-      <c r="B43" s="113"/>
-      <c r="C43" s="104" t="s">
+      <c r="B43" s="118"/>
+      <c r="C43" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="113"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
     </row>
     <row r="44" ht="25.5" spans="1:5">
-      <c r="A44" s="111">
+      <c r="A44" s="116">
         <v>11.2</v>
       </c>
-      <c r="B44" s="113"/>
-      <c r="C44" s="104" t="s">
+      <c r="B44" s="118"/>
+      <c r="C44" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="113"/>
-      <c r="E44" s="113"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
     </row>
     <row r="45" ht="25.5" spans="1:5">
-      <c r="A45" s="111">
+      <c r="A45" s="116">
         <v>11.3</v>
       </c>
-      <c r="B45" s="113"/>
-      <c r="C45" s="104" t="s">
+      <c r="B45" s="118"/>
+      <c r="C45" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="113"/>
-      <c r="E45" s="113"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="111">
+      <c r="A46" s="116">
         <v>12</v>
       </c>
-      <c r="B46" s="112" t="s">
+      <c r="B46" s="117" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="113"/>
-      <c r="D46" s="113"/>
-      <c r="E46" s="113"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="111">
+      <c r="A47" s="116">
         <v>12.1</v>
       </c>
-      <c r="B47" s="113"/>
-      <c r="C47" s="104" t="s">
+      <c r="B47" s="118"/>
+      <c r="C47" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="D47" s="113"/>
-      <c r="E47" s="113"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="111">
+      <c r="A48" s="116">
         <v>12.3</v>
       </c>
-      <c r="B48" s="113"/>
-      <c r="C48" s="104" t="s">
+      <c r="B48" s="118"/>
+      <c r="C48" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="D48" s="113"/>
-      <c r="E48" s="113"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="111">
+      <c r="A49" s="116">
         <v>12.4</v>
       </c>
-      <c r="B49" s="113"/>
-      <c r="C49" s="104" t="s">
+      <c r="B49" s="118"/>
+      <c r="C49" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="D49" s="113"/>
-      <c r="E49" s="113"/>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="111">
+      <c r="A50" s="116">
         <v>12.5</v>
       </c>
-      <c r="B50" s="113"/>
-      <c r="C50" s="115" t="s">
+      <c r="B50" s="118"/>
+      <c r="C50" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="113"/>
-      <c r="E50" s="113"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -4115,160 +4121,160 @@
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.4571428571429" style="102" customWidth="1"/>
-    <col min="2" max="2" width="32.4571428571429" style="103" customWidth="1"/>
+    <col min="1" max="1" width="30.4571428571429" style="107" customWidth="1"/>
+    <col min="2" max="2" width="32.4571428571429" style="108" customWidth="1"/>
     <col min="3" max="3" width="46.2666666666667" style="18" customWidth="1"/>
     <col min="4" max="16384" width="8.72380952380952" style="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="100"/>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="109" t="s">
         <v>76</v>
       </c>
       <c r="B2"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="109" t="s">
         <v>77</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="109" t="s">
         <v>78</v>
       </c>
       <c r="B4" s="45"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="109" t="s">
         <v>79</v>
       </c>
       <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="105"/>
+      <c r="B6" s="110"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="106"/>
+      <c r="B7" s="111"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="109" t="s">
         <v>82</v>
       </c>
       <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="109" t="s">
         <v>83</v>
       </c>
       <c r="B9" s="45"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="109" t="s">
         <v>84</v>
       </c>
       <c r="B10" s="45"/>
     </row>
     <row r="11" ht="25.5" spans="1:2">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="109" t="s">
         <v>85</v>
       </c>
       <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="109" t="s">
         <v>86</v>
       </c>
       <c r="B12" s="45"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="104"/>
+      <c r="B13" s="109"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="109"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="109" t="s">
         <v>89</v>
       </c>
       <c r="B15" s="45"/>
     </row>
     <row r="16" ht="25.5" spans="1:2">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="109" t="s">
         <v>90</v>
       </c>
       <c r="B16" s="45"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="104"/>
+      <c r="B17" s="109"/>
     </row>
     <row r="18" ht="25.5" spans="1:2">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="109" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="104"/>
+      <c r="B18" s="109"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="107" t="s">
+      <c r="A19" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="108">
+      <c r="B19" s="113">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="25.5" spans="1:2">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="104"/>
+      <c r="B20" s="109"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="104"/>
+      <c r="B21" s="109"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="109" t="s">
         <v>96</v>
       </c>
       <c r="B22" s="45"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="109" t="s">
         <v>97</v>
       </c>
       <c r="B23" s="45"/>
     </row>
     <row r="24" ht="25.5" spans="1:2">
-      <c r="A24" s="104" t="s">
+      <c r="A24" s="109" t="s">
         <v>98</v>
       </c>
       <c r="B24" s="45"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="109" t="s">
         <v>99</v>
       </c>
       <c r="B25" s="45"/>
@@ -4290,29 +4296,29 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="7.54285714285714" customWidth="1"/>
-    <col min="2" max="5" width="35.4571428571429" style="98" customWidth="1"/>
+    <col min="2" max="5" width="35.4571428571429" style="103" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:5">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="99"/>
+      <c r="B1" s="104"/>
     </row>
     <row r="2" ht="15.75" spans="1:5">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="105" t="s">
         <v>104</v>
       </c>
     </row>
@@ -4320,16 +4326,16 @@
       <c r="A3" s="62">
         <v>1</v>
       </c>
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="101" t="s">
+      <c r="D3" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="106" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4337,16 +4343,16 @@
       <c r="A4" s="62">
         <v>2</v>
       </c>
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="106" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="E4" s="106" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4354,16 +4360,16 @@
       <c r="A5" s="62">
         <v>3</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="106" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="101" t="s">
+      <c r="D5" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="101" t="s">
+      <c r="E5" s="106" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4371,16 +4377,16 @@
       <c r="A6" s="62">
         <v>4</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="106" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="101" t="s">
+      <c r="D6" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="106" t="s">
         <v>120</v>
       </c>
     </row>
@@ -4388,16 +4394,16 @@
       <c r="A7" s="62">
         <v>5</v>
       </c>
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="106" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="101" t="s">
+      <c r="C7" s="106" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="106" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="106" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4405,16 +4411,16 @@
       <c r="A8" s="62">
         <v>6</v>
       </c>
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="106" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="101" t="s">
+      <c r="D8" s="106" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="106" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4422,16 +4428,16 @@
       <c r="A9" s="62">
         <v>7</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="106" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="106" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="101" t="s">
+      <c r="D9" s="106" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="106" t="s">
         <v>132</v>
       </c>
     </row>
@@ -4439,16 +4445,16 @@
       <c r="A10" s="62">
         <v>8</v>
       </c>
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="101" t="s">
+      <c r="C10" s="106" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="101" t="s">
+      <c r="D10" s="106" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="106" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4456,16 +4462,16 @@
       <c r="A11" s="62">
         <v>9</v>
       </c>
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="101" t="s">
+      <c r="D11" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="106" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4473,16 +4479,16 @@
       <c r="A12" s="62">
         <v>10</v>
       </c>
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="106" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="106" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="101" t="s">
+      <c r="D12" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="106" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4505,38 +4511,45 @@
     <col min="2" max="2" width="62.1428571428571" style="93" customWidth="1"/>
     <col min="3" max="3" width="44.4285714285714" style="93" customWidth="1"/>
     <col min="4" max="4" width="29.1428571428571" style="93" customWidth="1"/>
-    <col min="5" max="5" width="59.7142857142857" style="94" customWidth="1"/>
-    <col min="6" max="6" width="9.42857142857143" customWidth="1"/>
-    <col min="8" max="16384" width="8.72380952380952" style="94"/>
+    <col min="5" max="5" width="11.4285714285714" style="94" customWidth="1"/>
+    <col min="6" max="6" width="14" style="95" customWidth="1"/>
+    <col min="7" max="7" width="57" style="96" customWidth="1"/>
+    <col min="8" max="16384" width="8.72380952380952" style="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="98" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1"/>
-      <c r="G1"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="99"/>
       <c r="H1"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="101" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="101" t="s">
         <v>148</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="101" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="E2" s="101" t="s">
         <v>150</v>
+      </c>
+      <c r="F2" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="101" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1"/>
@@ -4545,24 +4558,27 @@
       <c r="B10" s="93"/>
       <c r="C10" s="93"/>
       <c r="D10" s="93"/>
-      <c r="F10"/>
-      <c r="G10"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="96"/>
     </row>
     <row r="11" s="92" customFormat="1" spans="1:8">
       <c r="A11" s="93"/>
       <c r="B11" s="93"/>
       <c r="C11" s="93"/>
       <c r="D11" s="93"/>
-      <c r="F11"/>
-      <c r="G11"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="96"/>
     </row>
     <row r="12" s="92" customFormat="1" spans="1:8">
       <c r="A12" s="93"/>
       <c r="B12" s="93"/>
       <c r="C12" s="93"/>
       <c r="D12" s="93"/>
-      <c r="F12"/>
-      <c r="G12"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="96"/>
     </row>
     <row r="48" ht="31.5" customHeight="1"/>
     <row r="62" ht="31.5" customHeight="1"/>
@@ -4586,7 +4602,7 @@
     <row r="215" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
